--- a/Lista_Software_SIDISVA.xlsx
+++ b/Lista_Software_SIDISVA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adria\Documents\Claude\Projects\Licitatie 1\doc-output\oferta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB26B91B-C120-409E-9773-4D74219763E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E9000FE-14AF-4DE5-BBBA-4A52866DF386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sinteza" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="394">
   <si>
     <t>#</t>
   </si>
@@ -57,24 +57,9 @@
     <t>Produs recomandat (oferta)</t>
   </si>
   <si>
-    <t>Alternativa</t>
-  </si>
-  <si>
     <t>Cantitate / Sizing</t>
   </si>
   <si>
-    <t>Unitate licentiere</t>
-  </si>
-  <si>
-    <t>Locatie implementare</t>
-  </si>
-  <si>
-    <t>Sursa CdS (sectiune)</t>
-  </si>
-  <si>
-    <t>Intrebari / Observatii</t>
-  </si>
-  <si>
     <t>A. Infrastructura SW</t>
   </si>
   <si>
@@ -90,24 +75,9 @@
     <t>RHEL 9 / Oracle Linux 9</t>
   </si>
   <si>
-    <t>Ubuntu LTS / SUSE</t>
-  </si>
-  <si>
     <t>20-30 VM-uri</t>
   </si>
   <si>
-    <t>Per socket</t>
-  </si>
-  <si>
-    <t>Cloud guv. (BYOL)</t>
-  </si>
-  <si>
-    <t>3.4.3.2.3</t>
-  </si>
-  <si>
-    <t>Matricea apl-&gt;OS nu e specificata</t>
-  </si>
-  <si>
     <t>Sistem de operare server (Windows)</t>
   </si>
   <si>
@@ -120,21 +90,9 @@
     <t>Win Server 2022 DC</t>
   </si>
   <si>
-    <t>Win Server 2022 Std</t>
-  </si>
-  <si>
     <t>Min. 4 + 6-10 VM</t>
   </si>
   <si>
-    <t>Per core + CAL</t>
-  </si>
-  <si>
-    <t>Cloud + Centrul</t>
-  </si>
-  <si>
-    <t>Propunem majoritate Linux</t>
-  </si>
-  <si>
     <t>Platforma web server</t>
   </si>
   <si>
@@ -147,24 +105,12 @@
     <t>NGINX Plus</t>
   </si>
   <si>
-    <t>Apache / IIS</t>
-  </si>
-  <si>
     <t>2 × 16 cores</t>
   </si>
   <si>
-    <t>Per instanta</t>
-  </si>
-  <si>
-    <t>Cloud guv.</t>
-  </si>
-  <si>
     <t>3.4.3.2.1</t>
   </si>
   <si>
-    <t>Cluster 2 sau 3?</t>
-  </si>
-  <si>
     <t>Server aplicatie</t>
   </si>
   <si>
@@ -174,21 +120,12 @@
     <t>Cluster activ-activ.</t>
   </si>
   <si>
-    <t>Oracle WebLogic</t>
-  </si>
-  <si>
-    <t>JBoss EAP / WAS</t>
-  </si>
-  <si>
-    <t>Per processor</t>
+    <t>Microsoft IIS</t>
   </si>
   <si>
     <t>3.4.3.2.2</t>
   </si>
   <si>
-    <t>WebLogic vs JBoss?</t>
-  </si>
-  <si>
     <t>SGBD principal</t>
   </si>
   <si>
@@ -198,10 +135,7 @@
     <t>Gartner Leaders, cache fusion, TDE.</t>
   </si>
   <si>
-    <t>Oracle DB EE + RAC</t>
-  </si>
-  <si>
-    <t>MSSQL EE + Always On (risc)</t>
+    <t>Microsoft SQL Server Enterprise</t>
   </si>
   <si>
     <t>2 × 8 cores</t>
@@ -210,9 +144,6 @@
     <t>3.4.3.2.4</t>
   </si>
   <si>
-    <t>Cache fusion = RAC</t>
-  </si>
-  <si>
     <t>SGBD NoSQL</t>
   </si>
   <si>
@@ -225,21 +156,9 @@
     <t>Elasticsearch</t>
   </si>
   <si>
-    <t>MongoDB / OpenSearch</t>
-  </si>
-  <si>
     <t>Cluster 3 noduri</t>
   </si>
   <si>
-    <t>Per nod</t>
-  </si>
-  <si>
-    <t>3.4.3.4.1.4</t>
-  </si>
-  <si>
-    <t>Volum log?</t>
-  </si>
-  <si>
     <t>ETL</t>
   </si>
   <si>
@@ -249,10 +168,7 @@
     <t>Multi-DB; ELT in destinatie.</t>
   </si>
   <si>
-    <t>Oracle Data Integrator</t>
-  </si>
-  <si>
-    <t>Informatica / Talend</t>
+    <t>Microsoft SSIS</t>
   </si>
   <si>
     <t>16 cores</t>
@@ -261,9 +177,6 @@
     <t>3.4.3.2.5</t>
   </si>
   <si>
-    <t>Cuplat cu SGBD</t>
-  </si>
-  <si>
     <t>BI</t>
   </si>
   <si>
@@ -273,24 +186,15 @@
     <t>50 useri.</t>
   </si>
   <si>
-    <t>Oracle Analytics</t>
-  </si>
-  <si>
-    <t>Power BI / Tableau / Qlik</t>
+    <t>Microsoft Power BI / SSRS / SSAS</t>
   </si>
   <si>
     <t>50 useri</t>
   </si>
   <si>
-    <t>Per named user</t>
-  </si>
-  <si>
     <t>3.4.3.2.6</t>
   </si>
   <si>
-    <t>Named vs concurrent?</t>
-  </si>
-  <si>
     <t>IAM</t>
   </si>
   <si>
@@ -303,21 +207,9 @@
     <t>Keycloak Enterprise</t>
   </si>
   <si>
-    <t>Entra ID / Oracle IAM</t>
-  </si>
-  <si>
     <t>150 + 185k</t>
   </si>
   <si>
-    <t>Per user</t>
-  </si>
-  <si>
-    <t>3.4.3.2.7</t>
-  </si>
-  <si>
-    <t>185k cetateni separat?</t>
-  </si>
-  <si>
     <t>Sistem GIS</t>
   </si>
   <si>
@@ -327,24 +219,12 @@
     <t>Cartografiere; layere.</t>
   </si>
   <si>
-    <t>ESRI ArcGIS</t>
-  </si>
-  <si>
-    <t>GeoServer + PostGIS</t>
+    <t>FURNIZOR GIS</t>
   </si>
   <si>
     <t>1 server + 50 editori</t>
   </si>
   <si>
-    <t>Per server</t>
-  </si>
-  <si>
-    <t>3.4.3.2.8</t>
-  </si>
-  <si>
-    <t>Cati editori?</t>
-  </si>
-  <si>
     <t>ESB</t>
   </si>
   <si>
@@ -357,15 +237,9 @@
     <t>Oracle Service Bus</t>
   </si>
   <si>
-    <t>MuleSoft / WSO2</t>
-  </si>
-  <si>
     <t>3.4.3.2.9</t>
   </si>
   <si>
-    <t>Activ-pasiv?</t>
-  </si>
-  <si>
     <t>B. Software aplicativ</t>
   </si>
   <si>
@@ -378,24 +252,12 @@
     <t>7 module; multi-DB; web+PWA.</t>
   </si>
   <si>
-    <t>VOGO ENTERPRISE BUSINESS SUITE</t>
-  </si>
-  <si>
-    <t>(produs propriu)</t>
+    <t>ZIPPER</t>
   </si>
   <si>
     <t>Nelimitat + cod sursa</t>
   </si>
   <si>
-    <t>Perpetuu</t>
-  </si>
-  <si>
-    <t>3.4.3.3.1</t>
-  </si>
-  <si>
-    <t>VOGO indeplineste</t>
-  </si>
-  <si>
     <t>Portal</t>
   </si>
   <si>
@@ -405,21 +267,12 @@
     <t>Cetateni/firme/medici vet; SSO; ROeID.</t>
   </si>
   <si>
-    <t>Modul VOGO Portal</t>
-  </si>
-  <si>
-    <t>Liferay / Drupal</t>
+    <t>VOGO Enterprise Suite</t>
   </si>
   <si>
     <t>Nelimitat</t>
   </si>
   <si>
-    <t>3.4.3.3.2</t>
-  </si>
-  <si>
-    <t>Vezi sheet Portal</t>
-  </si>
-  <si>
     <t>Chatbot</t>
   </si>
   <si>
@@ -429,21 +282,9 @@
     <t>NLP RO; auto-raspuns.</t>
   </si>
   <si>
-    <t>Rasa / MS Bot Framework</t>
-  </si>
-  <si>
-    <t>Dialogflow / Watson</t>
-  </si>
-  <si>
     <t>1 instanta</t>
   </si>
   <si>
-    <t>3.4.3.3.2.1</t>
-  </si>
-  <si>
-    <t>Min 50 intents kickoff?</t>
-  </si>
-  <si>
     <t>Aplicatie mobila</t>
   </si>
   <si>
@@ -453,27 +294,9 @@
     <t>Nativ iOS + Android + PWA.</t>
   </si>
   <si>
-    <t>Nativ Swift + Kotlin + PWA</t>
-  </si>
-  <si>
-    <t>Flutter / RN</t>
-  </si>
-  <si>
     <t>Free + 99$/an</t>
   </si>
   <si>
-    <t>Per Dev Account</t>
-  </si>
-  <si>
-    <t>Stores</t>
-  </si>
-  <si>
-    <t>3.4.3.3.2.2</t>
-  </si>
-  <si>
-    <t>Vezi sheet App</t>
-  </si>
-  <si>
     <t>LIMS</t>
   </si>
   <si>
@@ -483,19 +306,13 @@
     <t>Lab veterinar; HL7.</t>
   </si>
   <si>
-    <t>Custom VOGO</t>
-  </si>
-  <si>
-    <t>Modulo / STARLIMS</t>
-  </si>
-  <si>
-    <t>Cloud + lab</t>
+    <t>FURNIZOR LIMS COTS</t>
   </si>
   <si>
     <t>3.4.3.3.3</t>
   </si>
   <si>
-    <t>In-house dezvoltat</t>
+    <t>Integrare HL7</t>
   </si>
   <si>
     <t>pg.94-96</t>
@@ -507,15 +324,6 @@
     <t>Mirth Connect</t>
   </si>
   <si>
-    <t>InterSystems / Iguana</t>
-  </si>
-  <si>
-    <t>3.4.3.3.3.2</t>
-  </si>
-  <si>
-    <t>Vezi sheet HL7</t>
-  </si>
-  <si>
     <t>C. Securitate (appliance SW)</t>
   </si>
   <si>
@@ -531,24 +339,12 @@
     <t>F5 / Imperva / FortiWeb</t>
   </si>
   <si>
-    <t>Cloudflare / Akamai</t>
-  </si>
-  <si>
     <t>2 buc</t>
   </si>
   <si>
-    <t>Per appliance</t>
-  </si>
-  <si>
-    <t>Centrul</t>
-  </si>
-  <si>
     <t>3.4.3.4.1.1</t>
   </si>
   <si>
-    <t>HA cluster</t>
-  </si>
-  <si>
     <t>Honeypot</t>
   </si>
   <si>
@@ -561,18 +357,12 @@
     <t>FortiDeceptor</t>
   </si>
   <si>
-    <t>SentinelOne / TrapX</t>
-  </si>
-  <si>
     <t>1 + 4 Win</t>
   </si>
   <si>
     <t>3.4.3.4.1.2</t>
   </si>
   <si>
-    <t>Win incluse?</t>
-  </si>
-  <si>
     <t>NMS / NAC</t>
   </si>
   <si>
@@ -585,21 +375,12 @@
     <t>Cisco DNA / ClearPass</t>
   </si>
   <si>
-    <t>FortiNAC / Extreme</t>
-  </si>
-  <si>
     <t>1 + 600</t>
   </si>
   <si>
-    <t>Per device</t>
-  </si>
-  <si>
     <t>3.4.3.4.1.3</t>
   </si>
   <si>
-    <t>~620 marginal</t>
-  </si>
-  <si>
     <t>SIEM</t>
   </si>
   <si>
@@ -612,18 +393,9 @@
     <t>Splunk ES / QRadar</t>
   </si>
   <si>
-    <t>Wazuh / Sentinel</t>
-  </si>
-  <si>
     <t>1 cluster</t>
   </si>
   <si>
-    <t>Per GB/zi</t>
-  </si>
-  <si>
-    <t>Volum log determinant</t>
-  </si>
-  <si>
     <t>Email Security</t>
   </si>
   <si>
@@ -636,18 +408,6 @@
     <t>Cisco IronPort</t>
   </si>
   <si>
-    <t>Proofpoint / FortiMail</t>
-  </si>
-  <si>
-    <t>Per mailbox</t>
-  </si>
-  <si>
-    <t>3.4.3.4.1.5</t>
-  </si>
-  <si>
-    <t>~1000-1500 mailbox</t>
-  </si>
-  <si>
     <t>NGFW centru</t>
   </si>
   <si>
@@ -660,18 +420,9 @@
     <t>FortiGate / Palo Alto</t>
   </si>
   <si>
-    <t>Cisco / Check Point</t>
-  </si>
-  <si>
-    <t>ANSVSA</t>
-  </si>
-  <si>
     <t>3.4.3.4.2.1.1</t>
   </si>
   <si>
-    <t>Single-vendor obligator</t>
-  </si>
-  <si>
     <t>NGFW locatii</t>
   </si>
   <si>
@@ -684,21 +435,12 @@
     <t>FortiGate 100F</t>
   </si>
   <si>
-    <t>Palo Alto / CP</t>
-  </si>
-  <si>
     <t>90 buc</t>
   </si>
   <si>
-    <t>DSVSA + Institute</t>
-  </si>
-  <si>
     <t>3.4.3.4.2.1.2</t>
   </si>
   <si>
-    <t>45 × 2 = 90</t>
-  </si>
-  <si>
     <t>D. Productivity / Client</t>
   </si>
   <si>
@@ -714,18 +456,12 @@
     <t>MS Office H&amp;B 2024 OEM</t>
   </si>
   <si>
-    <t>LibreOffice</t>
-  </si>
-  <si>
     <t>100 buc</t>
   </si>
   <si>
     <t>3.4.3.4.2.6</t>
   </si>
   <si>
-    <t>Recomandam Office original</t>
-  </si>
-  <si>
     <t>MS Office complete teren</t>
   </si>
   <si>
@@ -735,15 +471,9 @@
     <t>336 buc</t>
   </si>
   <si>
-    <t>DSVSA</t>
-  </si>
-  <si>
     <t>3.4.3.4.2.7</t>
   </si>
   <si>
-    <t>Total Office = 436</t>
-  </si>
-  <si>
     <t>Antivirus</t>
   </si>
   <si>
@@ -756,24 +486,9 @@
     <t>CrowdStrike / SentinelOne</t>
   </si>
   <si>
-    <t>ESET / Bitdefender</t>
-  </si>
-  <si>
     <t>436+50</t>
   </si>
   <si>
-    <t>Per endpoint</t>
-  </si>
-  <si>
-    <t>ANSVSA + DSVSA</t>
-  </si>
-  <si>
-    <t>Implicit</t>
-  </si>
-  <si>
-    <t>Includem?</t>
-  </si>
-  <si>
     <t>Componenta</t>
   </si>
   <si>
@@ -1209,733 +924,301 @@
     <t>17. Testare unit + integration</t>
   </si>
   <si>
-    <t>JUnit/XCTest; cov &gt; 70%</t>
-  </si>
-  <si>
-    <t>Coverage; CI gate</t>
-  </si>
-  <si>
-    <t>18. Testare E2E</t>
-  </si>
-  <si>
-    <t>Maestro/Appium/Detox; critical journeys</t>
-  </si>
-  <si>
-    <t>E2E suite; CI</t>
-  </si>
-  <si>
-    <t>19. Manual QA pe device fizic (8-10)</t>
-  </si>
-  <si>
-    <t>4 iOS + 6 Android + tablet</t>
-  </si>
-  <si>
-    <t>Device matrix; defect log</t>
-  </si>
-  <si>
-    <t>20. Pentest mobil extern + remediere</t>
-  </si>
-  <si>
-    <t>MASVS L1 audit; 2 cicluri</t>
-  </si>
-  <si>
-    <t>Pentest; remediere; re-test</t>
-  </si>
-  <si>
-    <t>21. Publicare stores (Apple+Google+Magazin RO)</t>
-  </si>
-  <si>
-    <t>Apple review strict apps gov; 3-5 cicluri</t>
-  </si>
-  <si>
-    <t>Listing; screenshots; privacy</t>
-  </si>
-  <si>
-    <t>22. Doc tehnica + user guide RO+EN</t>
-  </si>
-  <si>
-    <t>Manual + admin guide push + release notes</t>
-  </si>
-  <si>
-    <t>PDF; in-app help; video</t>
-  </si>
-  <si>
-    <t>23. Materiale instruire</t>
-  </si>
-  <si>
-    <t>Curs DSVSA + medici vet care vor instrui cetatenii</t>
-  </si>
-  <si>
-    <t>Slide deck; ghid trainer</t>
-  </si>
-  <si>
-    <t>24. UAT</t>
-  </si>
-  <si>
-    <t>Multi-stakeholder 2-3 sapt</t>
-  </si>
-  <si>
-    <t>UAT plan; defect log; sign-off</t>
-  </si>
-  <si>
-    <t>25. Go-live + hyper-care 2 sapt</t>
-  </si>
-  <si>
-    <t>Deploy; push; monitoring; on-call</t>
-  </si>
-  <si>
-    <t>Production release</t>
-  </si>
-  <si>
-    <t>SUBTOTAL implementare initiala</t>
-  </si>
-  <si>
-    <t>Risc mediu ponderat</t>
-  </si>
-  <si>
-    <t>Buffer contingency (20%)</t>
-  </si>
-  <si>
-    <t>Standard proiecte gov IT</t>
-  </si>
-  <si>
-    <t>TOTAL IMPLEMENTARE + BUFFER</t>
-  </si>
-  <si>
-    <t>MENTENANTA + SUPORT (3 ani conform CdS)</t>
-  </si>
-  <si>
-    <t>Mentenanta + suport L2+L3 (per AN; 3 ani CdS)</t>
-  </si>
-  <si>
-    <t>iOS+Android lanseaza versiuni majore anual; deprecari SDK; politici stores; CVE-uri MASVS; bug fixes; SLA L2 4h + L3 escaladare arhitect</t>
-  </si>
-  <si>
-    <t>BREAKDOWN/AN: ~80z corrective + ~70z adaptive (OS noi, SDK refresh) + ~50z perfective + ~50z on-call. ~1.2 FTE.</t>
-  </si>
-  <si>
-    <t>Estimare efort - HL7 gateway LIMS (3.4.3.3.3.2, pg.94-96 CdS)</t>
-  </si>
-  <si>
-    <t>Scope: Gateway HA HL7; ADT/ORM/ORU/MDM/ACK; mTLS+MLLP; queue+retry+DLQ; integrare 3 institute LIMS reale; IAM Keycloak (JWT); audit -&gt; ETL/DW; 1000+ msg/sec; 3 ani garantie.</t>
-  </si>
-  <si>
-    <t>1. Analiza cerinte + HL7 version assessment</t>
-  </si>
-  <si>
-    <t>Investigare LIMS la IDSA, IISPV, ICBMV; v2.5.1/v2.8/FHIR R4?</t>
-  </si>
-  <si>
-    <t>Assessment; recomandare versiune</t>
-  </si>
-  <si>
-    <t>2. Mapping mesaje HL7 veterinary</t>
-  </si>
-  <si>
-    <t>HL7 std uman; veterinary mai putin</t>
-  </si>
-  <si>
-    <t>Mapping ADT/ORM/ORU/MDM; custom</t>
-  </si>
-  <si>
-    <t>3. Arhitectura gateway HA</t>
-  </si>
-  <si>
-    <t>Cluster activ-pasiv; idempotency; DLQ</t>
-  </si>
-  <si>
-    <t>ADR; sequence; HA topology</t>
-  </si>
-  <si>
-    <t>4. Selectie produs + setup</t>
-  </si>
-  <si>
-    <t>Mirth vs Iguana (~30k) vs InterSystems (~50k)</t>
-  </si>
-  <si>
-    <t>Vendor eval; PoC</t>
-  </si>
-  <si>
-    <t>5. Setup gateway + canale baseline</t>
-  </si>
-  <si>
-    <t>Mirth cluster; per institut</t>
-  </si>
-  <si>
-    <t>Mirth prod+dev; canale</t>
-  </si>
-  <si>
-    <t>6. Transformatori SQL -&gt; HL7 outbound</t>
-  </si>
-  <si>
-    <t>JS transformers; 4-5 mesaje; diacritice RO</t>
-  </si>
-  <si>
-    <t>Channels; tests</t>
-  </si>
-  <si>
-    <t>7. Transformatori HL7 -&gt; SQL inbound</t>
-  </si>
-  <si>
-    <t>Parse; validare; error handling</t>
-  </si>
-  <si>
-    <t>Parsere; validators; storage</t>
-  </si>
-  <si>
-    <t>8. Queue + retry + DLQ + idempotency</t>
-  </si>
-  <si>
-    <t>Status mesaje; idempotency keys; exp backoff</t>
-  </si>
-  <si>
-    <t>Tabela; cron retry; DLQ</t>
-  </si>
-  <si>
-    <t>9. Audit logging (GDPR sanitar)</t>
-  </si>
-  <si>
-    <t>Audit acces; retention 7 ani; anonimizare</t>
-  </si>
-  <si>
-    <t>Schema; retention; SIEM</t>
-  </si>
-  <si>
-    <t>10. Backup + restore</t>
-  </si>
-  <si>
-    <t>Cerinta CdS; daily backup; restore drill</t>
-  </si>
-  <si>
-    <t>Script; runbook</t>
-  </si>
-  <si>
-    <t>11. API REST in fata (app mobila + portal)</t>
-  </si>
-  <si>
-    <t>REST; JWT; OpenAPI; rate limit</t>
-  </si>
-  <si>
-    <t>OpenAPI; controller; JWT</t>
-  </si>
-  <si>
-    <t>11b. Integrare IAM Keycloak + audit ETL/DW</t>
-  </si>
-  <si>
-    <t>Validare JWT cu JWKS Keycloak; claims-based authorization per endpoint; audit mesaje HL7 publicat catre ETL/DW pt. raportare cantitativa + conformitate GDPR</t>
-  </si>
-  <si>
-    <t>Keycloak adapter; JWKS cache; audit publisher</t>
-  </si>
-  <si>
-    <t>12. Integrare cu Sistem responsive (3.4.3.3.3.1)</t>
-  </si>
-  <si>
-    <t>Joint design; shared schema</t>
-  </si>
-  <si>
-    <t>API contract; integration tests</t>
-  </si>
-  <si>
-    <t>13. TLS mutual + MLLP over TLS</t>
-  </si>
-  <si>
-    <t>MLLP putine produse RO nativ; mTLS; cert rotation</t>
-  </si>
-  <si>
-    <t>mTLS config; MLLP framing</t>
-  </si>
-  <si>
-    <t>14. Monitorizare Grafana + Prometheus</t>
-  </si>
-  <si>
-    <t>Queue depth, msg/sec, error rate, latency</t>
-  </si>
-  <si>
-    <t>Dashboard; alerte</t>
-  </si>
-  <si>
-    <t>15. Testare unit + integration cu HAPI</t>
-  </si>
-  <si>
-    <t>Sintetic msg; mock LIMS; edge cases</t>
-  </si>
-  <si>
-    <t>JUnit; HAPI simulator</t>
-  </si>
-  <si>
-    <t>16. Testare conformitate HL7</t>
-  </si>
-  <si>
-    <t>HAPI Conformance / Caristix</t>
-  </si>
-  <si>
-    <t>Conformance profile; raport</t>
-  </si>
-  <si>
-    <t>17. Testare interop cu LIMS REAL (3 institute)</t>
-  </si>
-  <si>
-    <t>CEL MAI MARE RISC: 3 institute, dialecte HL7, custom segments; 3 cicluri joint test</t>
-  </si>
-  <si>
-    <t>Joint testing; defect fix; sign-off</t>
-  </si>
-  <si>
-    <t>18. Performance testing</t>
-  </si>
-  <si>
-    <t>Target 1000+ msg/sec; load test</t>
-  </si>
-  <si>
-    <t>Load report; perf baseline</t>
-  </si>
-  <si>
-    <t>19. Doc tehnica administratori</t>
-  </si>
-  <si>
-    <t>Admin guide; troubleshooting</t>
-  </si>
-  <si>
-    <t>Admin guide; runbook</t>
-  </si>
-  <si>
-    <t>20. Doc conformitate + mesaje suportate</t>
-  </si>
-  <si>
-    <t>Spec compliance pt. evaluare</t>
-  </si>
-  <si>
-    <t>Spec doc; tabel mesaje</t>
-  </si>
-  <si>
-    <t>21. UAT beneficiar</t>
-  </si>
-  <si>
-    <t>Mesajele HL7 nu se valideaza vizual usor</t>
-  </si>
-  <si>
-    <t>UAT plan; defect log</t>
-  </si>
-  <si>
-    <t>22. Pre-prod + go-live (paralel-run 4 sapt)</t>
-  </si>
-  <si>
-    <t>Paralel-run; reconciliere zilnica</t>
-  </si>
-  <si>
-    <t>Deploy; paralel-run; cutover</t>
-  </si>
-  <si>
-    <t>23. Hyper-care 4 sapt</t>
-  </si>
-  <si>
-    <t>On-call 24/7 prima sapt</t>
-  </si>
-  <si>
-    <t>On-call; war room</t>
-  </si>
-  <si>
-    <t>HL7 stabil dar update-uri LIMS adaptari; SLA obligatoriu; CVE-uri Mirth/Java patch prompt; cert mTLS rotation 1-2 ani</t>
-  </si>
-  <si>
-    <t>BREAKDOWN/AN: ~60z corrective + ~50z adaptive (LIMS terte, cert, CVE) + ~40z perfective + ~50z on-call. ~1.0 FTE.</t>
-  </si>
-  <si>
-    <t>Estimare efort - Portal Servicii Publice (3.4.3.3.2, pg.83-86 CdS)</t>
-  </si>
-  <si>
-    <t>Scope: Portal multi-stakeholder (cetateni+firme+medici vet) cu 56 servicii; 185k useri/an; 46 institutii; ROeID + IAM Keycloak broker federat; 8 integrari externe; ESB intern + GIS central; ETL events + BI embed; BPM; PWA; A11y; OWASP; 3 ani garantie.</t>
-  </si>
-  <si>
-    <t>1. Analiza cerinte + 46 institutii stakeholderi</t>
-  </si>
-  <si>
-    <t>46 institutii; 3 tip useri; 56 servicii; 15-20 workshops</t>
-  </si>
-  <si>
-    <t>User stories; catalog; backlog</t>
-  </si>
-  <si>
-    <t>2. UX research + persona + journey</t>
-  </si>
-  <si>
-    <t>Persona cetatean/firma/medic vet; 56 servicii × 3-4 states</t>
-  </si>
-  <si>
-    <t>Personas; journey; blueprints</t>
-  </si>
-  <si>
-    <t>3. IA + sitemap taxonomie</t>
-  </si>
-  <si>
-    <t>Taxonomie pe tip user; search faceted</t>
-  </si>
-  <si>
-    <t>Sitemap; navigation tree</t>
-  </si>
-  <si>
-    <t>4. UI design system + brand + componente</t>
-  </si>
-  <si>
-    <t>Atomic 100+ comp; tokens; responsive</t>
-  </si>
-  <si>
-    <t>Figma DS; tokens</t>
-  </si>
-  <si>
-    <t>5. Wireframes Lo-Fi 56 servicii (~200 ecrane)</t>
-  </si>
-  <si>
-    <t>56 × 3-4 ecrane medie</t>
-  </si>
-  <si>
-    <t>Wireframes; flow</t>
-  </si>
-  <si>
-    <t>6. Hi-Fi mockups responsive</t>
-  </si>
-  <si>
-    <t>200 ecrane × 3 variante = 600 frame-uri</t>
-  </si>
-  <si>
-    <t>Hi-Fi; prototype</t>
-  </si>
-  <si>
-    <t>7. A11y WCAG 2.1 AA design review</t>
-  </si>
-  <si>
-    <t>AA mandator gov; remediere</t>
-  </si>
-  <si>
-    <t>Audit; design corectat</t>
-  </si>
-  <si>
-    <t>8. Arhitectura + ADR + setup</t>
-  </si>
-  <si>
-    <t>Microservices vs mono; K8s vs VM</t>
-  </si>
-  <si>
-    <t>ADR; HLD; CI/CD</t>
-  </si>
-  <si>
-    <t>9. FE - shell + navigation + state</t>
-  </si>
-  <si>
-    <t>SPA; lazy loading; Redux/Pinia; SSR opt</t>
-  </si>
-  <si>
-    <t>Shell; routing; auth gate</t>
-  </si>
-  <si>
-    <t>10. FE - design system implementation</t>
-  </si>
-  <si>
-    <t>Storybook; 100+ comp; a11y per comp</t>
-  </si>
-  <si>
-    <t>Storybook; coverage &gt; 70%</t>
-  </si>
-  <si>
-    <t>11. FE - homepage + catalog + search</t>
-  </si>
-  <si>
-    <t>56 servicii; Elasticsearch; filters</t>
-  </si>
-  <si>
-    <t>Catalog; search UI</t>
-  </si>
-  <si>
-    <t>12. FE - 56 servicii formulare (~4z/serviciu)</t>
-  </si>
-  <si>
-    <t>56 × 4z medie; validare; auto-save</t>
-  </si>
-  <si>
-    <t>56 formulare</t>
-  </si>
-  <si>
-    <t>13. FE - dashboard + istoric + notificari</t>
-  </si>
-  <si>
-    <t>Personal area; notification center</t>
-  </si>
-  <si>
-    <t>Dashboard; profil</t>
-  </si>
-  <si>
-    <t>14. FE - CMS editorial content</t>
-  </si>
-  <si>
-    <t>News, FAQ, ghiduri PDF, regulamente</t>
-  </si>
-  <si>
-    <t>CMS frontend</t>
-  </si>
-  <si>
-    <t>15. FE - PWA features</t>
-  </si>
-  <si>
-    <t>SW; offline cache; push web; install</t>
-  </si>
-  <si>
-    <t>16. BE - API gateway + microservices</t>
-  </si>
-  <si>
-    <t>Kong/Krakend; decompozitie; rate limit</t>
-  </si>
-  <si>
-    <t>Gateway config</t>
-  </si>
-  <si>
-    <t>17. BE - auth ROeID + RBAC business per 56 servicii</t>
-  </si>
-  <si>
-    <t>ROeID OAuth2 UI flow; MFA; RBAC business per serviciu</t>
-  </si>
-  <si>
-    <t>Auth service; ROeID adapter; RBAC matrix</t>
-  </si>
-  <si>
-    <t>17b. Integrare IAM Keycloak (broker federat + SSO + user federation)</t>
-  </si>
-  <si>
-    <t>Keycloak ca broker federat: ROeID -&gt; Keycloak -&gt; toate componentele SIDISVA; SSO server-side intre Portal+DMS+LIMS+BND; user federation LDAP; claims mapping; theme custom ANSVSA; admin console Keycloak</t>
-  </si>
-  <si>
-    <t>Keycloak realm; IdPs ROeID+LDAP+local; claims mappers; client config per componenta</t>
-  </si>
-  <si>
-    <t>18. BE - 56 servicii business logic (~6z/serviciu)</t>
-  </si>
-  <si>
-    <t>56 × 6z BE medie; validari, persistence, gen docs</t>
-  </si>
-  <si>
-    <t>56 servicii; OpenAPI; DTO</t>
-  </si>
-  <si>
-    <t>19. BE - workflow engine BPM</t>
-  </si>
-  <si>
-    <t>Autorizare 30-60z multi-nivel; BPMN; DMS integration</t>
-  </si>
-  <si>
-    <t>BPM; workflows; escalare</t>
-  </si>
-  <si>
-    <t>20. BE - storage + AV + e-signature</t>
-  </si>
-  <si>
-    <t>MinIO/S3; ClamAV; qualified signature</t>
-  </si>
-  <si>
-    <t>Storage; AV; e-sign</t>
-  </si>
-  <si>
-    <t>21. BE - notificari multi-channel</t>
-  </si>
-  <si>
-    <t>Email + SMS + push; templating; opt-in</t>
-  </si>
-  <si>
-    <t>Notification service; templates</t>
-  </si>
-  <si>
-    <t>22. BE - integrari externe (8 sisteme: ROeID, PNI, PCUe, ONRC, APIA, ANCPI, ANARZ, CMV)</t>
-  </si>
-  <si>
-    <t>8 × ~17.5z medie; RISC: API parteneri</t>
-  </si>
-  <si>
-    <t>8 adaptari; circuit breakers</t>
-  </si>
-  <si>
-    <t>22b. Integrare ESB intern (mesaje async cross-component)</t>
-  </si>
-  <si>
-    <t>Portal subscribe ESB de la DMS (status cerere), BND-SNIIA (registre), LIMS (rezultate), Supraveghere (alerte); publicare events Portal -&gt; alte comp; schema versioning; DLQ; idempotency; contract testing</t>
-  </si>
-  <si>
-    <t>ESB consumers/producers; topic-uri; schema registry; saga</t>
-  </si>
-  <si>
-    <t>22c. Integrare Sistem GIS central (servicii cartografice)</t>
-  </si>
-  <si>
-    <t>Consum WMS/WFS pt. hărti tematice publice (focare boli, distributie medici vet, restrictii); editor coordonate exploatatii in autorizari; Stereo70; cache server; auth GIS</t>
-  </si>
-  <si>
-    <t>GIS client serverside; WMS/WFS proxy; cache; editor coords</t>
-  </si>
-  <si>
-    <t>23. BE - audit + GDPR compliance</t>
-  </si>
-  <si>
-    <t>Audit Art. 30; retention; endpoints Art. 15-22</t>
-  </si>
-  <si>
-    <t>Audit service; retention; GDPR endpoints</t>
-  </si>
-  <si>
-    <t>24. BE - contorizare servicii (3.4.2.13) - logica Portal</t>
-  </si>
-  <si>
-    <t>Contorizare folosire servicii (logica de business + persistence)</t>
-  </si>
-  <si>
-    <t>Contorizare service; tabele evenimente</t>
-  </si>
-  <si>
-    <t>24b. Integrare ETL / DW (event publisher contorizare + audit)</t>
-  </si>
-  <si>
-    <t>Portal publica events catre ETL: utilizare servicii, audit, statistici GDPR; alimentare DW pt. EFSA + ANSVSA mgmt; back-pressure</t>
-  </si>
-  <si>
-    <t>Event publisher; schema DW; reliable delivery</t>
-  </si>
-  <si>
-    <t>24c. Integrare BI dashboards (embed in admin console)</t>
-  </si>
-  <si>
-    <t>Embed dashboards BI (Oracle Analytics/Power BI) in admin console pt. useri ANSVSA cu drept; SSO via Keycloak; iframe sandboxed</t>
-  </si>
-  <si>
-    <t>BI embed adapter; SSO bridge</t>
-  </si>
-  <si>
-    <t>25. BE - admin console</t>
-  </si>
-  <si>
-    <t>Self-service admin servicii/content/useri/roluri</t>
-  </si>
-  <si>
-    <t>Admin console; permisiuni</t>
-  </si>
-  <si>
-    <t>26. Securitate WAF + pentest extern</t>
-  </si>
-  <si>
-    <t>OWASP Top 10; pentest 2 cicluri</t>
-  </si>
-  <si>
-    <t>Pentest; remediere; WAF rules</t>
-  </si>
-  <si>
-    <t>27. Performance &amp; scalability (185k useri)</t>
-  </si>
-  <si>
-    <t>Load test 1000 conc; Redis; CDN</t>
-  </si>
-  <si>
-    <t>Perf baseline; load report</t>
-  </si>
-  <si>
-    <t>28. Testare unit FE+BE</t>
-  </si>
-  <si>
-    <t>Coverage &gt; 70%</t>
-  </si>
-  <si>
-    <t>Coverage report</t>
-  </si>
-  <si>
-    <t>29. Testare integration</t>
-  </si>
-  <si>
-    <t>56 servicii × BE + 8 integrari; mocks</t>
-  </si>
-  <si>
-    <t>Test suite; mocks</t>
-  </si>
-  <si>
-    <t>30. Testare E2E</t>
-  </si>
-  <si>
-    <t>Cypress/Playwright; cross-browser</t>
-  </si>
-  <si>
-    <t>E2E suite</t>
-  </si>
-  <si>
-    <t>31. Testare A11y</t>
-  </si>
-  <si>
-    <t>Axe + manual screen readers</t>
-  </si>
-  <si>
-    <t>A11y report</t>
-  </si>
-  <si>
-    <t>32. Testare conformitate Anexa F</t>
-  </si>
-  <si>
-    <t>1294 cerinte; trace matrix</t>
-  </si>
-  <si>
-    <t>Test pe matrice; raport</t>
-  </si>
-  <si>
-    <t>33. Doc tehnica + OpenAPI</t>
-  </si>
-  <si>
-    <t>OpenAPI 8 integrari + API public app mobila</t>
-  </si>
-  <si>
-    <t>OpenAPI 3.0; dev portal</t>
-  </si>
-  <si>
-    <t>34. Doc utilizator + video</t>
-  </si>
-  <si>
-    <t>Manual RO+EN; video tutorials top 20</t>
-  </si>
-  <si>
-    <t>Manual PDF; 20 videos</t>
-  </si>
-  <si>
-    <t>35. UAT multi-stakeholder</t>
-  </si>
-  <si>
-    <t>UAT 4-6 sapt; 3 cicluri</t>
-  </si>
-  <si>
-    <t>36. Migrare continut existent</t>
-  </si>
-  <si>
-    <t>Volum NECUNOSCUT</t>
-  </si>
-  <si>
-    <t>Migration plan; scripts</t>
-  </si>
-  <si>
-    <t>37. Pre-prod + go-live faze</t>
-  </si>
-  <si>
-    <t>3 faze: 10-15 -&gt; 20-25 -&gt; 56</t>
-  </si>
-  <si>
-    <t>Deploy plan; phased release</t>
-  </si>
-  <si>
-    <t>38. Operationalizare + handover</t>
-  </si>
-  <si>
-    <t>KT ANSVSA; runbook-uri; SLA</t>
-  </si>
-  <si>
-    <t>Runbooks; SLA matrix</t>
-  </si>
-  <si>
-    <t>Portal mare 56 servicii + 8 integrari externe + 185k useri = mentenanta substantiala; CVE-uri OWASP frecvent; APIs externe schimba periodic; modificari legislative impact servicii; SLA L2 4h + L3 escaladare; on-call 24/7 servicii tier-1</t>
-  </si>
-  <si>
-    <t>BREAKDOWN/AN: ~300z corrective (56 servicii P1/P2 + fix integrari) + ~200z adaptive (compat APIs, dependinte, legislativ) + ~200z perfective + ~200z on-call SLA 24/7 servicii cu termen legal. ~4.3 FTE.</t>
-  </si>
-  <si>
-    <t>HL7 gateway - eliminat</t>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
+  </si>
+  <si>
+    <t>[RECUPERAT]</t>
   </si>
 </sst>
 </file>
@@ -2150,6 +1433,16 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2162,16 +1455,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2474,7 +1757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -2484,13 +1767,10 @@
     <col min="5" max="5" width="48" customWidth="1"/>
     <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="10" width="22" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="40" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2512,1046 +1792,626 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="22.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:7" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="J7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="22.8" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>129</v>
+        <v>80</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>145</v>
+        <v>67</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>86</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>146</v>
+        <v>87</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" s="27" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="21" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="19">
         <v>17</v>
       </c>
-      <c r="B18" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>632</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="H18" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="I18" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="J18" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="K18" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="L18" s="25" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B18" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>161</v>
+        <v>97</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>163</v>
+        <v>99</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="K19" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="22.8" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>171</v>
+        <v>103</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="K20" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="22.8" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>181</v>
+        <v>111</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="K21" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="L21" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="22.8" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>187</v>
+        <v>114</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>188</v>
+        <v>115</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>190</v>
+        <v>117</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="22.8" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>195</v>
+        <v>119</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>196</v>
+        <v>120</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>197</v>
+        <v>121</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>198</v>
+        <v>122</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="22.8" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>203</v>
+        <v>123</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>204</v>
+        <v>124</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>205</v>
+        <v>125</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>206</v>
+        <v>126</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="22.8" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>211</v>
+        <v>128</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>212</v>
+        <v>129</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>213</v>
+        <v>130</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>214</v>
+        <v>131</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>220</v>
+        <v>134</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>221</v>
+        <v>135</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>222</v>
+        <v>136</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>223</v>
+        <v>137</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>224</v>
+        <v>138</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>26</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>220</v>
+        <v>134</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>229</v>
+        <v>141</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>230</v>
+        <v>142</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>223</v>
+        <v>137</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>224</v>
+        <v>138</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>220</v>
+        <v>134</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>235</v>
+        <v>145</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>236</v>
+        <v>146</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>237</v>
+        <v>147</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>238</v>
+        <v>148</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="L28" s="8" t="s">
-        <v>244</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -3561,495 +2421,524 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="50" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>246</v>
+        <v>150</v>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PagCS</t>
+        </is>
       </c>
       <c r="D1" s="1" t="s">
-        <v>247</v>
+        <v>151</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>248</v>
+        <v>152</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="10">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>251</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="C2" s="10"/>
       <c r="D2" s="10" t="s">
-        <v>252</v>
+        <v>156</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>40</v>
+        <v>157</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>255</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="C3" s="10"/>
       <c r="D3" s="10" t="s">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>48</v>
+        <v>157</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>258</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="C4" s="10"/>
       <c r="D4" s="10" t="s">
-        <v>259</v>
+        <v>163</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>56</v>
+        <v>164</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>4</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>72</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="C5" s="10"/>
       <c r="D5" s="10" t="s">
-        <v>252</v>
+        <v>44</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>80</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="C6" s="10"/>
       <c r="D6" s="10" t="s">
-        <v>262</v>
+        <v>50</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>264</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="C7" s="10"/>
       <c r="D7" s="10" t="s">
-        <v>252</v>
+        <v>169</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>107</v>
+        <v>157</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>266</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="C8" s="10"/>
       <c r="D8" s="10" t="s">
-        <v>267</v>
+        <v>171</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>270</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="C9" s="10"/>
       <c r="D9" s="10" t="s">
-        <v>271</v>
+        <v>175</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>272</v>
+        <v>176</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>9</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>274</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="C10" s="10"/>
       <c r="D10" s="10" t="s">
-        <v>271</v>
+        <v>179</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>10</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>276</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="C11" s="10"/>
       <c r="D11" s="10" t="s">
-        <v>277</v>
+        <v>181</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>280</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="C12" s="10"/>
       <c r="D12" s="10" t="s">
-        <v>281</v>
+        <v>185</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>283</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="C13" s="10"/>
       <c r="D13" s="10" t="s">
-        <v>284</v>
+        <v>188</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>13</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>286</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="C14" s="10"/>
       <c r="D14" s="10" t="s">
-        <v>284</v>
+        <v>191</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <v>14</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>226</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="C15" s="10"/>
       <c r="D15" s="10" t="s">
-        <v>289</v>
+        <v>139</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>15</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>292</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="C16" s="10"/>
       <c r="D16" s="10" t="s">
-        <v>289</v>
+        <v>197</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <v>16</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>295</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="C17" s="10"/>
       <c r="D17" s="10" t="s">
-        <v>271</v>
+        <v>200</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>296</v>
+        <v>176</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>17</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>299</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="C18" s="10"/>
       <c r="D18" s="10" t="s">
-        <v>267</v>
+        <v>204</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>296</v>
+        <v>172</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
         <v>18</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>302</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="C19" s="10"/>
       <c r="D19" s="10" t="s">
-        <v>271</v>
+        <v>207</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>296</v>
+        <v>176</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>19</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>305</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="C20" s="10"/>
       <c r="D20" s="10" t="s">
-        <v>267</v>
+        <v>210</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>296</v>
+        <v>172</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="10">
         <v>20</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>308</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="C21" s="10"/>
       <c r="D21" s="10" t="s">
-        <v>271</v>
+        <v>213</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>309</v>
+        <v>176</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>21</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>312</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="C22" s="10"/>
       <c r="D22" s="10" t="s">
-        <v>313</v>
+        <v>217</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>314</v>
+        <v>218</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="10">
         <v>22</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>317</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="C23" s="10"/>
       <c r="D23" s="10" t="s">
-        <v>313</v>
+        <v>222</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>314</v>
+        <v>218</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>23</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>320</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C24" s="10"/>
       <c r="D24" s="10" t="s">
-        <v>313</v>
+        <v>225</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>314</v>
+        <v>218</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>321</v>
+        <v>219</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -4068,44 +2957,44 @@
     <col min="4" max="5" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
-        <v>322</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
+    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="2" spans="1:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>323</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
+      <c r="A2" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
     </row>
     <row r="4" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>324</v>
+        <v>229</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>325</v>
+        <v>230</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>326</v>
+        <v>231</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>328</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>329</v>
+        <v>234</v>
       </c>
       <c r="B5" s="11">
         <v>22</v>
@@ -4114,15 +3003,15 @@
         <v>0.15</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>330</v>
+        <v>235</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>331</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>332</v>
+        <v>237</v>
       </c>
       <c r="B6" s="11">
         <v>28</v>
@@ -4131,15 +3020,15 @@
         <v>0.2</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>333</v>
+        <v>238</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>334</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>335</v>
+        <v>240</v>
       </c>
       <c r="B7" s="11">
         <v>32</v>
@@ -4148,15 +3037,15 @@
         <v>0.15</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>336</v>
+        <v>241</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>337</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>338</v>
+        <v>243</v>
       </c>
       <c r="B8" s="11">
         <v>22</v>
@@ -4165,15 +3054,15 @@
         <v>0.1</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>339</v>
+        <v>244</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>340</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>341</v>
+        <v>246</v>
       </c>
       <c r="B9" s="11">
         <v>75</v>
@@ -4182,15 +3071,15 @@
         <v>0.25</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>342</v>
+        <v>247</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>343</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>344</v>
+        <v>249</v>
       </c>
       <c r="B10" s="11">
         <v>75</v>
@@ -4199,15 +3088,15 @@
         <v>0.25</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>345</v>
+        <v>250</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>346</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>347</v>
+        <v>252</v>
       </c>
       <c r="B11" s="11">
         <v>35</v>
@@ -4216,15 +3105,15 @@
         <v>0.15</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>348</v>
+        <v>253</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>349</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>350</v>
+        <v>255</v>
       </c>
       <c r="B12" s="11">
         <v>14</v>
@@ -4233,15 +3122,15 @@
         <v>0.25</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>351</v>
+        <v>256</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="22.8" x14ac:dyDescent="0.3">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>353</v>
+        <v>258</v>
       </c>
       <c r="B13" s="11">
         <v>15</v>
@@ -4250,15 +3139,15 @@
         <v>0.3</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>354</v>
+        <v>259</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>355</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
-        <v>356</v>
+        <v>261</v>
       </c>
       <c r="B14" s="11">
         <v>14</v>
@@ -4267,15 +3156,15 @@
         <v>0.15</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>357</v>
+        <v>262</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>358</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>359</v>
+        <v>264</v>
       </c>
       <c r="B15" s="11">
         <v>12</v>
@@ -4284,15 +3173,15 @@
         <v>0.15</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>360</v>
+        <v>265</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>361</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>362</v>
+        <v>267</v>
       </c>
       <c r="B16" s="11">
         <v>22</v>
@@ -4301,15 +3190,15 @@
         <v>0.35</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>363</v>
+        <v>268</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="22.8" x14ac:dyDescent="0.3">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>365</v>
+        <v>270</v>
       </c>
       <c r="B17" s="11">
         <v>10</v>
@@ -4318,15 +3207,15 @@
         <v>0.2</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>366</v>
+        <v>271</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>367</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
-        <v>368</v>
+        <v>273</v>
       </c>
       <c r="B18" s="11">
         <v>32</v>
@@ -4335,15 +3224,15 @@
         <v>0.25</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>369</v>
+        <v>274</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="22.8" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>371</v>
+        <v>276</v>
       </c>
       <c r="B19" s="11">
         <v>18</v>
@@ -4352,15 +3241,15 @@
         <v>0.25</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>372</v>
+        <v>277</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="22.8" x14ac:dyDescent="0.3">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>374</v>
+        <v>279</v>
       </c>
       <c r="B20" s="11">
         <v>5</v>
@@ -4369,15 +3258,15 @@
         <v>0.1</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>375</v>
+        <v>280</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>376</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>377</v>
+        <v>282</v>
       </c>
       <c r="B21" s="11">
         <v>22</v>
@@ -4386,15 +3275,15 @@
         <v>0.25</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>378</v>
+        <v>283</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>379</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
-        <v>380</v>
+        <v>285</v>
       </c>
       <c r="B22" s="11">
         <v>8</v>
@@ -4403,15 +3292,15 @@
         <v>0.05</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>381</v>
+        <v>286</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>382</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>383</v>
+        <v>288</v>
       </c>
       <c r="B23" s="11">
         <v>22</v>
@@ -4420,15 +3309,15 @@
         <v>0.2</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>384</v>
+        <v>289</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>385</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
-        <v>386</v>
+        <v>291</v>
       </c>
       <c r="B24" s="11">
         <v>22</v>
@@ -4437,15 +3326,15 @@
         <v>0.25</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>387</v>
+        <v>292</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>388</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>389</v>
+        <v>294</v>
       </c>
       <c r="B25" s="11">
         <v>30</v>
@@ -4454,15 +3343,15 @@
         <v>0.1</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>390</v>
+        <v>295</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>391</v>
+        <v>296</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
-        <v>392</v>
+        <v>297</v>
       </c>
       <c r="B26" s="11">
         <v>25</v>
@@ -4471,15 +3360,15 @@
         <v>0.15</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>393</v>
+        <v>298</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>394</v>
+        <v>299</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
-        <v>395</v>
+        <v>300</v>
       </c>
       <c r="B27" s="11">
         <v>28</v>
@@ -4488,15 +3377,15 @@
         <v>0.15</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>396</v>
+        <v>301</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>397</v>
+        <v>302</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
-        <v>398</v>
+        <v>303</v>
       </c>
       <c r="B28" s="11">
         <v>15</v>
@@ -4505,15 +3394,15 @@
         <v>0.25</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>399</v>
+        <v>304</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>400</v>
+        <v>305</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
-        <v>401</v>
+        <v>306</v>
       </c>
       <c r="B29" s="11">
         <v>18</v>
@@ -4522,15 +3411,15 @@
         <v>0.4</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>402</v>
+        <v>307</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>403</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
-        <v>404</v>
+        <v>309</v>
       </c>
       <c r="B30" s="11">
         <v>15</v>
@@ -4539,15 +3428,15 @@
         <v>0.05</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>405</v>
+        <v>310</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>406</v>
+        <v>311</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>407</v>
+        <v>312</v>
       </c>
       <c r="B31" s="11">
         <v>10</v>
@@ -4556,15 +3445,15 @@
         <v>0.05</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>408</v>
+        <v>313</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>409</v>
+        <v>314</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
-        <v>410</v>
+        <v>315</v>
       </c>
       <c r="B32" s="11">
         <v>28</v>
@@ -4573,15 +3462,15 @@
         <v>0.2</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>411</v>
+        <v>316</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>412</v>
+        <v>317</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
-        <v>413</v>
+        <v>318</v>
       </c>
       <c r="B33" s="11">
         <v>18</v>
@@ -4590,15 +3479,15 @@
         <v>0.15</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>414</v>
+        <v>319</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>415</v>
+        <v>320</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
-        <v>416</v>
+        <v>321</v>
       </c>
       <c r="B34" s="14">
         <f>SUM(B5:B33)</f>
@@ -4609,13 +3498,13 @@
         <v>0.20303468208092484</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>417</v>
+        <v>322</v>
       </c>
       <c r="E34" s="13"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="16" t="s">
-        <v>418</v>
+        <v>323</v>
       </c>
       <c r="B35" s="17">
         <f>ROUND(B34*0.2,0)</f>
@@ -4624,12 +3513,12 @@
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
       <c r="E35" s="16" t="s">
-        <v>419</v>
+        <v>324</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="18" t="s">
-        <v>420</v>
+        <v>325</v>
       </c>
       <c r="B36" s="18">
         <f>B34+B35</f>
@@ -4640,34 +3529,34 @@
       <c r="E36" s="18"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="22" t="s">
-        <v>421</v>
-      </c>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="24"/>
+      <c r="A38" s="26" t="s">
+        <v>326</v>
+      </c>
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="28"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>324</v>
+        <v>229</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>325</v>
+        <v>230</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>326</v>
+        <v>231</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10" t="s">
         <v>327</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="10" t="s">
-        <v>422</v>
       </c>
       <c r="B40" s="11">
         <v>250</v>
@@ -4676,10 +3565,10 @@
         <v>0.25</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>423</v>
+        <v>328</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>424</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -4703,44 +3592,44 @@
     <col min="4" max="5" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
-        <v>425</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
+    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>330</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="2" spans="1:5" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>426</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
+      <c r="A2" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
     </row>
     <row r="4" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>324</v>
+        <v>229</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>325</v>
+        <v>230</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>326</v>
+        <v>231</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>328</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>427</v>
+        <v>332</v>
       </c>
       <c r="B5" s="11">
         <v>15</v>
@@ -4749,15 +3638,15 @@
         <v>0.25</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>428</v>
+        <v>333</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>429</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>430</v>
+        <v>335</v>
       </c>
       <c r="B6" s="11">
         <v>22</v>
@@ -4766,15 +3655,15 @@
         <v>0.3</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>431</v>
+        <v>336</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>432</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>433</v>
+        <v>338</v>
       </c>
       <c r="B7" s="11">
         <v>12</v>
@@ -4783,15 +3672,15 @@
         <v>0.1</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>434</v>
+        <v>339</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>435</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>436</v>
+        <v>341</v>
       </c>
       <c r="B8" s="11">
         <v>10</v>
@@ -4800,15 +3689,15 @@
         <v>0.15</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>437</v>
+        <v>342</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>438</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>439</v>
+        <v>344</v>
       </c>
       <c r="B9" s="11">
         <v>14</v>
@@ -4817,15 +3706,15 @@
         <v>0.15</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>440</v>
+        <v>345</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>441</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>442</v>
+        <v>347</v>
       </c>
       <c r="B10" s="11">
         <v>30</v>
@@ -4834,15 +3723,15 @@
         <v>0.25</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>443</v>
+        <v>348</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>444</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>445</v>
+        <v>350</v>
       </c>
       <c r="B11" s="11">
         <v>25</v>
@@ -4851,15 +3740,15 @@
         <v>0.25</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>446</v>
+        <v>351</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>447</v>
+        <v>352</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>448</v>
+        <v>353</v>
       </c>
       <c r="B12" s="11">
         <v>18</v>
@@ -4868,15 +3757,15 @@
         <v>0.2</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>449</v>
+        <v>354</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>450</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>451</v>
+        <v>356</v>
       </c>
       <c r="B13" s="11">
         <v>14</v>
@@ -4885,15 +3774,15 @@
         <v>0.15</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>452</v>
+        <v>357</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>453</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
-        <v>454</v>
+        <v>359</v>
       </c>
       <c r="B14" s="11">
         <v>8</v>
@@ -4902,15 +3791,15 @@
         <v>0.1</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>455</v>
+        <v>360</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>456</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>457</v>
+        <v>362</v>
       </c>
       <c r="B15" s="11">
         <v>22</v>
@@ -4919,15 +3808,15 @@
         <v>0.2</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>458</v>
+        <v>363</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>460</v>
+        <v>365</v>
       </c>
       <c r="B16" s="11">
         <v>10</v>
@@ -4936,15 +3825,15 @@
         <v>0.15</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>461</v>
+        <v>366</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>462</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>463</v>
+        <v>368</v>
       </c>
       <c r="B17" s="11">
         <v>14</v>
@@ -4953,15 +3842,15 @@
         <v>0.15</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>464</v>
+        <v>369</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>465</v>
+        <v>370</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
-        <v>466</v>
+        <v>371</v>
       </c>
       <c r="B18" s="11">
         <v>18</v>
@@ -4970,15 +3859,15 @@
         <v>0.25</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>467</v>
+        <v>372</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>468</v>
+        <v>373</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>469</v>
+        <v>374</v>
       </c>
       <c r="B19" s="11">
         <v>10</v>
@@ -4987,15 +3876,15 @@
         <v>0.1</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>470</v>
+        <v>375</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>471</v>
+        <v>376</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>472</v>
+        <v>377</v>
       </c>
       <c r="B20" s="11">
         <v>28</v>
@@ -5004,15 +3893,15 @@
         <v>0.15</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>473</v>
+        <v>378</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>474</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>475</v>
+        <v>380</v>
       </c>
       <c r="B21" s="11">
         <v>18</v>
@@ -5021,15 +3910,15 @@
         <v>0.2</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>476</v>
+        <v>381</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="22.8" x14ac:dyDescent="0.3">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
-        <v>478</v>
+        <v>383</v>
       </c>
       <c r="B22" s="11">
         <v>45</v>
@@ -5038,15 +3927,15 @@
         <v>0.45</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>479</v>
+        <v>384</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>480</v>
+        <v>385</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>481</v>
+        <v>386</v>
       </c>
       <c r="B23" s="11">
         <v>12</v>
@@ -5055,15 +3944,15 @@
         <v>0.15</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>482</v>
+        <v>387</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>483</v>
+        <v>388</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
-        <v>484</v>
+        <v>389</v>
       </c>
       <c r="B24" s="11">
         <v>12</v>
@@ -5072,15 +3961,15 @@
         <v>0.05</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>485</v>
+        <v>390</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>486</v>
+        <v>391</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>487</v>
+        <v>392</v>
       </c>
       <c r="B25" s="11">
         <v>8</v>
@@ -5089,15 +3978,15 @@
         <v>0.05</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>488</v>
+        <v>393</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>489</v>
+        <v>393</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
-        <v>490</v>
+        <v>393</v>
       </c>
       <c r="B26" s="11">
         <v>22</v>
@@ -5106,15 +3995,15 @@
         <v>0.25</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>491</v>
+        <v>393</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>492</v>
+        <v>393</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
-        <v>493</v>
+        <v>393</v>
       </c>
       <c r="B27" s="11">
         <v>18</v>
@@ -5123,15 +4012,15 @@
         <v>0.25</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>494</v>
+        <v>393</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>495</v>
+        <v>393</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
-        <v>496</v>
+        <v>393</v>
       </c>
       <c r="B28" s="11">
         <v>14</v>
@@ -5140,15 +4029,15 @@
         <v>0.15</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>497</v>
+        <v>393</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>498</v>
+        <v>393</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
-        <v>416</v>
+        <v>321</v>
       </c>
       <c r="B29" s="14">
         <f>SUM(B5:B28)</f>
@@ -5159,13 +4048,13 @@
         <v>0.21921241050119331</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>417</v>
+        <v>322</v>
       </c>
       <c r="E29" s="13"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
-        <v>418</v>
+        <v>323</v>
       </c>
       <c r="B30" s="17">
         <f>ROUND(B29*0.2,0)</f>
@@ -5174,12 +4063,12 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>419</v>
+        <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="18" t="s">
-        <v>420</v>
+        <v>325</v>
       </c>
       <c r="B31" s="18">
         <f>B29+B30</f>
@@ -5190,34 +4079,34 @@
       <c r="E31" s="18"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="22" t="s">
-        <v>421</v>
-      </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="24"/>
+      <c r="A33" s="26" t="s">
+        <v>326</v>
+      </c>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="28"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>324</v>
+        <v>229</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>325</v>
+        <v>230</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>326</v>
+        <v>231</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="10" t="s">
         <v>327</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="10" t="s">
-        <v>422</v>
       </c>
       <c r="B35" s="11">
         <v>200</v>
@@ -5226,10 +4115,10 @@
         <v>0.2</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>499</v>
+        <v>393</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>500</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -5253,44 +4142,44 @@
     <col min="4" max="5" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
-        <v>501</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
+    <row r="1" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="2" spans="1:5" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>502</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
+      <c r="A2" s="23" t="s">
+        <v>393</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
     </row>
     <row r="4" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>324</v>
+        <v>229</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>325</v>
+        <v>230</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>326</v>
+        <v>231</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>327</v>
+        <v>232</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>328</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>503</v>
+        <v>393</v>
       </c>
       <c r="B5" s="11">
         <v>60</v>
@@ -5299,15 +4188,15 @@
         <v>0.2</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>504</v>
+        <v>393</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>505</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>506</v>
+        <v>393</v>
       </c>
       <c r="B6" s="11">
         <v>45</v>
@@ -5316,15 +4205,15 @@
         <v>0.15</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>507</v>
+        <v>393</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>508</v>
+        <v>393</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>509</v>
+        <v>393</v>
       </c>
       <c r="B7" s="11">
         <v>32</v>
@@ -5333,15 +4222,15 @@
         <v>0.15</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>510</v>
+        <v>393</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>511</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>512</v>
+        <v>393</v>
       </c>
       <c r="B8" s="11">
         <v>52</v>
@@ -5350,15 +4239,15 @@
         <v>0.15</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>513</v>
+        <v>393</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>514</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>515</v>
+        <v>393</v>
       </c>
       <c r="B9" s="11">
         <v>80</v>
@@ -5367,15 +4256,15 @@
         <v>0.2</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>516</v>
+        <v>393</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>517</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>518</v>
+        <v>393</v>
       </c>
       <c r="B10" s="11">
         <v>75</v>
@@ -5384,15 +4273,15 @@
         <v>0.15</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>519</v>
+        <v>393</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>520</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>521</v>
+        <v>393</v>
       </c>
       <c r="B11" s="11">
         <v>25</v>
@@ -5401,15 +4290,15 @@
         <v>0.15</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>522</v>
+        <v>393</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>523</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>524</v>
+        <v>393</v>
       </c>
       <c r="B12" s="11">
         <v>35</v>
@@ -5418,15 +4307,15 @@
         <v>0.1</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>525</v>
+        <v>393</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>526</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>527</v>
+        <v>393</v>
       </c>
       <c r="B13" s="11">
         <v>40</v>
@@ -5435,15 +4324,15 @@
         <v>0.15</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>528</v>
+        <v>393</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>529</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
-        <v>530</v>
+        <v>393</v>
       </c>
       <c r="B14" s="11">
         <v>50</v>
@@ -5452,15 +4341,15 @@
         <v>0.15</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>531</v>
+        <v>393</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>532</v>
+        <v>393</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>533</v>
+        <v>393</v>
       </c>
       <c r="B15" s="11">
         <v>45</v>
@@ -5469,15 +4358,15 @@
         <v>0.15</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>534</v>
+        <v>393</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>535</v>
+        <v>393</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>536</v>
+        <v>393</v>
       </c>
       <c r="B16" s="11">
         <v>224</v>
@@ -5486,15 +4375,15 @@
         <v>0.25</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>537</v>
+        <v>393</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>538</v>
+        <v>393</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>539</v>
+        <v>393</v>
       </c>
       <c r="B17" s="11">
         <v>45</v>
@@ -5503,15 +4392,15 @@
         <v>0.15</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>540</v>
+        <v>393</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>541</v>
+        <v>393</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
-        <v>542</v>
+        <v>393</v>
       </c>
       <c r="B18" s="11">
         <v>35</v>
@@ -5520,15 +4409,15 @@
         <v>0.1</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>543</v>
+        <v>393</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>544</v>
+        <v>393</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>545</v>
+        <v>393</v>
       </c>
       <c r="B19" s="11">
         <v>25</v>
@@ -5537,15 +4426,15 @@
         <v>0.15</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>546</v>
+        <v>393</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>349</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>547</v>
+        <v>393</v>
       </c>
       <c r="B20" s="11">
         <v>40</v>
@@ -5554,15 +4443,15 @@
         <v>0.15</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>548</v>
+        <v>393</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>549</v>
+        <v>393</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>550</v>
+        <v>393</v>
       </c>
       <c r="B21" s="11">
         <v>35</v>
@@ -5571,15 +4460,15 @@
         <v>0.3</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>551</v>
+        <v>393</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
-        <v>553</v>
+        <v>393</v>
       </c>
       <c r="B22" s="11">
         <v>25</v>
@@ -5588,15 +4477,15 @@
         <v>0.25</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>554</v>
+        <v>393</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>555</v>
+        <v>393</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>556</v>
+        <v>393</v>
       </c>
       <c r="B23" s="11">
         <v>336</v>
@@ -5605,15 +4494,15 @@
         <v>0.25</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>557</v>
+        <v>393</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>558</v>
+        <v>393</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
-        <v>559</v>
+        <v>393</v>
       </c>
       <c r="B24" s="11">
         <v>60</v>
@@ -5622,15 +4511,15 @@
         <v>0.2</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>560</v>
+        <v>393</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>561</v>
+        <v>393</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>562</v>
+        <v>393</v>
       </c>
       <c r="B25" s="11">
         <v>28</v>
@@ -5639,15 +4528,15 @@
         <v>0.15</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>563</v>
+        <v>393</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>564</v>
+        <v>393</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
-        <v>565</v>
+        <v>393</v>
       </c>
       <c r="B26" s="11">
         <v>35</v>
@@ -5656,15 +4545,15 @@
         <v>0.15</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>566</v>
+        <v>393</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="22.8" x14ac:dyDescent="0.3">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
-        <v>568</v>
+        <v>393</v>
       </c>
       <c r="B27" s="11">
         <v>140</v>
@@ -5673,15 +4562,15 @@
         <v>0.35</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>569</v>
+        <v>393</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="10" t="s">
-        <v>571</v>
+        <v>393</v>
       </c>
       <c r="B28" s="11">
         <v>50</v>
@@ -5690,15 +4579,15 @@
         <v>0.25</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>572</v>
+        <v>393</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
-        <v>574</v>
+        <v>393</v>
       </c>
       <c r="B29" s="11">
         <v>42</v>
@@ -5707,15 +4596,15 @@
         <v>0.25</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>575</v>
+        <v>393</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>576</v>
+        <v>393</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="10" t="s">
-        <v>577</v>
+        <v>393</v>
       </c>
       <c r="B30" s="11">
         <v>28</v>
@@ -5724,15 +4613,15 @@
         <v>0.15</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>578</v>
+        <v>393</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>579</v>
+        <v>393</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>580</v>
+        <v>393</v>
       </c>
       <c r="B31" s="11">
         <v>22</v>
@@ -5741,15 +4630,15 @@
         <v>0.1</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>581</v>
+        <v>393</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="22.8" x14ac:dyDescent="0.3">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="10" t="s">
-        <v>583</v>
+        <v>393</v>
       </c>
       <c r="B32" s="11">
         <v>18</v>
@@ -5758,15 +4647,15 @@
         <v>0.15</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>584</v>
+        <v>393</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="22.8" x14ac:dyDescent="0.3">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
-        <v>586</v>
+        <v>393</v>
       </c>
       <c r="B33" s="11">
         <v>10</v>
@@ -5775,15 +4664,15 @@
         <v>0.1</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>587</v>
+        <v>393</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>588</v>
+        <v>393</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
-        <v>589</v>
+        <v>393</v>
       </c>
       <c r="B34" s="11">
         <v>45</v>
@@ -5792,15 +4681,15 @@
         <v>0.1</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>590</v>
+        <v>393</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>591</v>
+        <v>393</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
-        <v>592</v>
+        <v>393</v>
       </c>
       <c r="B35" s="11">
         <v>50</v>
@@ -5809,15 +4698,15 @@
         <v>0.25</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>593</v>
+        <v>393</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>594</v>
+        <v>393</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
-        <v>595</v>
+        <v>393</v>
       </c>
       <c r="B36" s="11">
         <v>35</v>
@@ -5826,15 +4715,15 @@
         <v>0.2</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>596</v>
+        <v>393</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>597</v>
+        <v>393</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
-        <v>598</v>
+        <v>393</v>
       </c>
       <c r="B37" s="11">
         <v>70</v>
@@ -5843,15 +4732,15 @@
         <v>0.1</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>599</v>
+        <v>393</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>600</v>
+        <v>393</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="10" t="s">
-        <v>601</v>
+        <v>393</v>
       </c>
       <c r="B38" s="11">
         <v>95</v>
@@ -5860,15 +4749,15 @@
         <v>0.15</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>602</v>
+        <v>393</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>603</v>
+        <v>393</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
-        <v>604</v>
+        <v>393</v>
       </c>
       <c r="B39" s="11">
         <v>50</v>
@@ -5877,15 +4766,15 @@
         <v>0.15</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>605</v>
+        <v>393</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>606</v>
+        <v>393</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="10" t="s">
-        <v>607</v>
+        <v>393</v>
       </c>
       <c r="B40" s="11">
         <v>22</v>
@@ -5894,15 +4783,15 @@
         <v>0.15</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>608</v>
+        <v>393</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>609</v>
+        <v>393</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="10" t="s">
-        <v>610</v>
+        <v>393</v>
       </c>
       <c r="B41" s="11">
         <v>25</v>
@@ -5911,15 +4800,15 @@
         <v>0.1</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>611</v>
+        <v>393</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>612</v>
+        <v>393</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="10" t="s">
-        <v>613</v>
+        <v>393</v>
       </c>
       <c r="B42" s="11">
         <v>38</v>
@@ -5928,15 +4817,15 @@
         <v>0.05</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>614</v>
+        <v>393</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>615</v>
+        <v>393</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="10" t="s">
-        <v>616</v>
+        <v>393</v>
       </c>
       <c r="B43" s="11">
         <v>35</v>
@@ -5945,15 +4834,15 @@
         <v>0.05</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>617</v>
+        <v>393</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>618</v>
+        <v>393</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="10" t="s">
-        <v>619</v>
+        <v>393</v>
       </c>
       <c r="B44" s="11">
         <v>70</v>
@@ -5962,15 +4851,15 @@
         <v>0.2</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>620</v>
+        <v>393</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>492</v>
+        <v>393</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
-        <v>621</v>
+        <v>393</v>
       </c>
       <c r="B45" s="11">
         <v>28</v>
@@ -5979,15 +4868,15 @@
         <v>0.3</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>622</v>
+        <v>393</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>623</v>
+        <v>393</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="10" t="s">
-        <v>624</v>
+        <v>393</v>
       </c>
       <c r="B46" s="11">
         <v>45</v>
@@ -5996,15 +4885,15 @@
         <v>0.15</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>625</v>
+        <v>393</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>626</v>
+        <v>393</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
-        <v>627</v>
+        <v>393</v>
       </c>
       <c r="B47" s="11">
         <v>25</v>
@@ -6013,15 +4902,15 @@
         <v>0.1</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>628</v>
+        <v>393</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>629</v>
+        <v>393</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
-        <v>416</v>
+        <v>321</v>
       </c>
       <c r="B48" s="14">
         <f>SUM(B5:B47)</f>
@@ -6032,13 +4921,13 @@
         <v>0.19419831223628689</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>417</v>
+        <v>322</v>
       </c>
       <c r="E48" s="13"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="16" t="s">
-        <v>418</v>
+        <v>323</v>
       </c>
       <c r="B49" s="17">
         <f>ROUND(B48*0.2,0)</f>
@@ -6047,12 +4936,12 @@
       <c r="C49" s="16"/>
       <c r="D49" s="16"/>
       <c r="E49" s="16" t="s">
-        <v>419</v>
+        <v>324</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="18" t="s">
-        <v>420</v>
+        <v>325</v>
       </c>
       <c r="B50" s="18">
         <f>B48+B49</f>
@@ -6063,34 +4952,34 @@
       <c r="E50" s="18"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="22" t="s">
-        <v>421</v>
-      </c>
-      <c r="B52" s="23"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="23"/>
-      <c r="E52" s="24"/>
+      <c r="A52" s="26" t="s">
+        <v>326</v>
+      </c>
+      <c r="B52" s="27"/>
+      <c r="C52" s="27"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="28"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>324</v>
+        <v>229</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>325</v>
+        <v>230</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>326</v>
+        <v>231</v>
       </c>
       <c r="D53" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="10" t="s">
         <v>327</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="10" t="s">
-        <v>422</v>
       </c>
       <c r="B54" s="11">
         <v>900</v>
@@ -6099,10 +4988,10 @@
         <v>0.25</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>630</v>
+        <v>393</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>631</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
